--- a/beacon/public/sample-data.xlsx
+++ b/beacon/public/sample-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/djdiptayan/Documents/Developer/Beacon/beacon/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D3D524-055B-A441-A243-A3539BED06AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B0D1E8-99DB-3047-BA2E-49DA6642EFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="21400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="800" windowWidth="36000" windowHeight="21360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contacts" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
   <si>
     <t>Name</t>
   </si>
@@ -37,7 +37,16 @@
     <t>Bob Johnson</t>
   </si>
   <si>
-    <t>djdiptayan1@gmail.com</t>
+    <t>dj2037@srmist.edu.in</t>
+  </si>
+  <si>
+    <t>John Doe1</t>
+  </si>
+  <si>
+    <t>Jane Smith1</t>
+  </si>
+  <si>
+    <t>Bob Johnson1</t>
   </si>
 </sst>
 </file>
@@ -425,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -460,11 +469,34 @@
         <v>5</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{503D8ED4-5181-CE46-BBCF-04E06FBE3C6E}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{9BAB4A23-01A9-6D4C-A933-0EF2A8F5733C}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{FBA76588-C3F5-9C43-AA28-B7ECD125BEB0}"/>
+    <hyperlink ref="B5" r:id="rId2" xr:uid="{7CC387C8-E958-B049-B5CA-05A9ADBFFB9F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
